--- a/lab_meeting/lab_meeting_calendar.xlsx
+++ b/lab_meeting/lab_meeting_calendar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcmedu-my.sharepoint.com/personal/u244834_bcm_edu/Documents/lab/websites/frankfort-lab/lab_meeting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62E1F7D-A7EA-4095-92AF-7A1CCBB8E4DD}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B543AF-E442-47B3-B031-AC022727E74B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>Reagan, Ritu, Miles, Molly, Grace</t>
-  </si>
-  <si>
-    <t>Ben Frankfort &amp; Daniel Brock</t>
   </si>
 </sst>
 </file>
@@ -1131,16 +1128,13 @@
         <v>46062</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1170,6 +1164,9 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1204,7 +1201,7 @@
         <v>46097</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/lab_meeting/lab_meeting_calendar.xlsx
+++ b/lab_meeting/lab_meeting_calendar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcmedu-my.sharepoint.com/personal/u244834_bcm_edu/Documents/lab/websites/frankfort-lab/lab_meeting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B543AF-E442-47B3-B031-AC022727E74B}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52A77DD-CB0F-4308-BE9C-56752DBE39E4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
+    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -186,15 +186,6 @@
     <t>Soumi Mitra</t>
   </si>
   <si>
-    <t>Rice finals</t>
-  </si>
-  <si>
-    <t>Kevin Wu</t>
-  </si>
-  <si>
-    <t>Giselle Gonzalez</t>
-  </si>
-  <si>
     <t>Joy Kim</t>
   </si>
   <si>
@@ -205,6 +196,21 @@
   </si>
   <si>
     <t>Reagan, Ritu, Miles, Molly, Grace</t>
+  </si>
+  <si>
+    <t>Kevin Wu &amp; Giselle Gonzalez</t>
+  </si>
+  <si>
+    <t>Change time to 9:30</t>
+  </si>
+  <si>
+    <t>No Meeting - ARVO</t>
+  </si>
+  <si>
+    <t>ARVO Poster review - abstracts</t>
+  </si>
+  <si>
+    <t>ARVO recap</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8914FEE5-3B14-4065-9F37-64FFCCDB3E85}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -1117,7 +1123,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1215,13 +1221,13 @@
         <v>46104</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,7 +1235,7 @@
         <v>46111</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -1253,9 +1259,6 @@
       <c r="A15" s="2">
         <v>46125</v>
       </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
@@ -1265,7 +1268,7 @@
         <v>46132</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1275,48 +1278,128 @@
       <c r="A17" s="2">
         <v>46139</v>
       </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2">
+        <v>46167</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2">
+        <v>46174</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2">
+        <v>46181</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2">
+        <v>46188</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2">
+        <v>46195</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2">
+        <v>46223</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>46230</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lab_meeting/lab_meeting_calendar.xlsx
+++ b/lab_meeting/lab_meeting_calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcmedu-my.sharepoint.com/personal/u244834_bcm_edu/Documents/lab/websites/frankfort-lab/lab_meeting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52A77DD-CB0F-4308-BE9C-56752DBE39E4}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB9E118-D560-4C76-979E-A7B266F29DCC}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -211,6 +211,15 @@
   </si>
   <si>
     <t>ARVO recap</t>
+  </si>
+  <si>
+    <t>Memorial Day</t>
+  </si>
+  <si>
+    <t>Benjamin Frankfort</t>
+  </si>
+  <si>
+    <t>Guofu &amp; Salim</t>
   </si>
 </sst>
 </file>
@@ -1325,14 +1334,23 @@
       <c r="A21" s="2">
         <v>46167</v>
       </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
       <c r="E21" t="b">
         <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46174</v>
       </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
@@ -1341,6 +1359,9 @@
       <c r="A23" s="2">
         <v>46181</v>
       </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
@@ -1349,6 +1370,9 @@
       <c r="A24" s="2">
         <v>46188</v>
       </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
@@ -1356,6 +1380,9 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46195</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>

--- a/lab_meeting/lab_meeting_calendar.xlsx
+++ b/lab_meeting/lab_meeting_calendar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcmedu-my.sharepoint.com/personal/u244834_bcm_edu/Documents/lab/websites/frankfort-lab/lab_meeting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB9E118-D560-4C76-979E-A7B266F29DCC}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="8_{B3463328-A060-409B-801D-1A35AED95DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9883BCB2-BA16-4C1D-BFE1-FA5A3ABA403F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{148D7F30-F220-420D-858E-D08D52631B38}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -220,6 +220,21 @@
   </si>
   <si>
     <t>Guofu &amp; Salim</t>
+  </si>
+  <si>
+    <t>lab cleaning</t>
+  </si>
+  <si>
+    <t>fridge cleaning</t>
+  </si>
+  <si>
+    <t>lab move</t>
+  </si>
+  <si>
+    <t>freezer move</t>
+  </si>
+  <si>
+    <t>Move to North Carolina!</t>
   </si>
 </sst>
 </file>
@@ -602,17 +617,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA943D-9A62-40D0-B0BF-8802F5644FD8}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.84375" customWidth="1"/>
+    <col min="2" max="2" width="17.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="4" max="4" width="22.53515625" customWidth="1"/>
+    <col min="5" max="5" width="18.84375" customWidth="1"/>
+    <col min="6" max="6" width="13.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,7 +650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45838</v>
       </c>
@@ -647,7 +662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f>A2+7</f>
         <v>45845</v>
@@ -660,7 +675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A9" si="0">A3+7</f>
         <v>45852</v>
@@ -679,7 +694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>45859</v>
@@ -698,7 +713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>45866</v>
@@ -714,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>45873</v>
@@ -727,7 +742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>45880</v>
@@ -740,7 +755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>45887</v>
@@ -756,7 +771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45894</v>
       </c>
@@ -774,7 +789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f>A10+7</f>
         <v>45901</v>
@@ -787,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f t="shared" ref="A12:A16" si="1">A11+7</f>
         <v>45908</v>
@@ -803,7 +818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f t="shared" si="1"/>
         <v>45915</v>
@@ -819,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45926</v>
       </c>
@@ -837,7 +852,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45929</v>
       </c>
@@ -852,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="1"/>
         <v>45936</v>
@@ -868,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45943</v>
       </c>
@@ -886,7 +901,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45950</v>
       </c>
@@ -898,7 +913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45957</v>
       </c>
@@ -916,7 +931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45964</v>
       </c>
@@ -931,7 +946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45971</v>
       </c>
@@ -946,7 +961,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45978</v>
       </c>
@@ -961,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45981</v>
       </c>
@@ -976,7 +991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45985</v>
       </c>
@@ -988,7 +1003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45992</v>
       </c>
@@ -1003,7 +1018,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45999</v>
       </c>
@@ -1012,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>46006</v>
       </c>
@@ -1021,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>46013</v>
       </c>
@@ -1033,7 +1048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>46020</v>
       </c>
@@ -1053,16 +1068,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8914FEE5-3B14-4065-9F37-64FFCCDB3E85}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.84375" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="4" max="4" width="18.84375" customWidth="1"/>
+    <col min="5" max="5" width="13.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>46034</v>
       </c>
@@ -1096,7 +1111,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>46041</v>
       </c>
@@ -1110,7 +1125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>46048</v>
       </c>
@@ -1124,7 +1139,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>46055</v>
       </c>
@@ -1138,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>46062</v>
       </c>
@@ -1152,7 +1167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>46069</v>
       </c>
@@ -1166,7 +1181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>46076</v>
       </c>
@@ -1183,7 +1198,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>46083</v>
       </c>
@@ -1197,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>46090</v>
       </c>
@@ -1211,7 +1226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>46097</v>
       </c>
@@ -1225,7 +1240,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>46104</v>
       </c>
@@ -1239,7 +1254,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>46111</v>
       </c>
@@ -1250,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>46118</v>
       </c>
@@ -1264,7 +1279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>46125</v>
       </c>
@@ -1272,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>46132</v>
       </c>
@@ -1283,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>46139</v>
       </c>
@@ -1297,7 +1312,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>46146</v>
       </c>
@@ -1308,7 +1323,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>46153</v>
       </c>
@@ -1319,7 +1334,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>46160</v>
       </c>
@@ -1330,7 +1345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>46167</v>
       </c>
@@ -1344,7 +1359,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>46174</v>
       </c>
@@ -1355,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>46181</v>
       </c>
@@ -1366,7 +1381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>46188</v>
       </c>
@@ -1377,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>46195</v>
       </c>
@@ -1388,41 +1403,56 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>46202</v>
       </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>46209</v>
       </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>46216</v>
       </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>46223</v>
       </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>46230</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
